--- a/data/trans_dic/IP16A01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,68; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,86; 81,26</t>
+          <t>44,57; 80,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,31; 67,15</t>
+          <t>28,22; 69,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,52; 65,74</t>
+          <t>34,17; 65,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,22; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,3; 83,78</t>
+          <t>50,46; 83,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,79; 72,03</t>
+          <t>32,51; 71,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,27; 71,06</t>
+          <t>39,46; 73,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>96,7; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,43; 78,55</t>
+          <t>54,71; 78,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,85; 63,91</t>
+          <t>36,26; 63,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,26; 64,73</t>
+          <t>40,74; 65,04</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,64; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,24; 87,72</t>
+          <t>58,73; 88,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,08; 84,75</t>
+          <t>41,34; 84,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,9; 79,67</t>
+          <t>46,34; 78,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,19; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,7; 82,67</t>
+          <t>35,02; 82,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,03; 82,53</t>
+          <t>44,63; 81,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,88; 85,0</t>
+          <t>53,07; 84,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96,64; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57,18; 81,16</t>
+          <t>57,47; 82,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,21; 78,06</t>
+          <t>49,71; 78,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,87; 78,43</t>
+          <t>54,19; 78,05</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,65; 94,53</t>
+          <t>58,24; 94,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,95; 93,1</t>
+          <t>42,56; 91,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,85; 77,83</t>
+          <t>31,17; 78,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,22; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,84; 94,08</t>
+          <t>54,37; 94,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,48; 81,17</t>
+          <t>24,9; 76,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,9; 70,56</t>
+          <t>29,61; 71,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96,18; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,86; 90,85</t>
+          <t>63,26; 91,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,76; 78,24</t>
+          <t>45,52; 80,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,67; 66,71</t>
+          <t>33,53; 67,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,64; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,13; 67,86</t>
+          <t>45,87; 69,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,84; 71,43</t>
+          <t>48,68; 71,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,7; 88,58</t>
+          <t>38,69; 87,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,76; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,71; 67,38</t>
+          <t>45,12; 66,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 59,02</t>
+          <t>31,99; 58,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,68; 72,49</t>
+          <t>46,14; 72,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>98,33; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,74; 64,38</t>
+          <t>49,37; 65,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,1; 63,62</t>
+          <t>45,17; 62,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,06; 82,14</t>
+          <t>48,93; 81,96</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>93,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,11; 79,47</t>
+          <t>51,67; 80,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,1; 75,16</t>
+          <t>40,98; 73,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,59; 69,97</t>
+          <t>40,53; 70,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,84; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,95; 79,61</t>
+          <t>53,23; 81,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,46; 80,12</t>
+          <t>49,3; 80,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,87; 71,35</t>
+          <t>43,18; 70,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>97,05; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57,09; 76,69</t>
+          <t>56,01; 77,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,41; 74,63</t>
+          <t>51,0; 73,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,78; 67,31</t>
+          <t>45,89; 66,94</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,94; 90,75</t>
+          <t>30,88; 90,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,81; 86,41</t>
+          <t>46,49; 88,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,96; 67,72</t>
+          <t>21,79; 69,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,73; 79,94</t>
+          <t>34,03; 78,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,88; 67,8</t>
+          <t>18,47; 68,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,2; 74,38</t>
+          <t>25,19; 72,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44,41; 78,34</t>
+          <t>45,32; 79,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,87; 72,91</t>
+          <t>41,14; 74,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,94; 64,28</t>
+          <t>31,86; 63,59</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>98,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60,05; 72,42</t>
+          <t>59,1; 72,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52,95; 66,99</t>
+          <t>52,95; 66,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,87; 74,06</t>
+          <t>48,57; 75,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,05; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,01; 69,22</t>
+          <t>55,82; 68,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,26; 61,53</t>
+          <t>46,77; 61,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,63; 65,88</t>
+          <t>51,09; 65,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>99,48; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,75; 68,86</t>
+          <t>59,97; 69,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52,47; 62,63</t>
+          <t>52,28; 62,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,83; 68,89</t>
+          <t>52,6; 68,07</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>15171</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13586</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7288</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12421</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15125</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9360</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>17788</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28711</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16648</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>30209</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9325; 16922</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4470; 11003</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8491; 16317</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11089; 18357</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5769; 12724</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>12392; 22967</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>23471; 33541</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12180; 21214</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>22918; 36587</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>19430</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17237</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7708</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15051</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7340</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12443</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16481</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>37287</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24578</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20150</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>31533</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13450; 20337</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4959; 10083</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10858; 18454</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4233; 9992</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8508; 15599</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12467; 19961</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>20110; 28716</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>15439; 24455</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>25427; 36625</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9416</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6460</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9623</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8478</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>33062</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19039</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11964</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>13622</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6681; 10845</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3765; 8130</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2991; 7579</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6785; 11741</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2557; 7853</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5121; 12296</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15151; 21798</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8699; 15341</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9017; 18231</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>37685</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27370</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28129</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48928</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33220</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15587</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>34541</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>76475</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>60591</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>43716</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>83468</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>21898; 32969</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22629; 33156</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>29548; 66925</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>26583; 39110</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>11044; 20176</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>25769; 40354</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>52648; 69513</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>36597; 50450</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>64704; 108373</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>18853</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19320</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>16004</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19059</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17061</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>20534</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>42752</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38380</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>32551</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>36538</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14802; 23060</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10909; 19667</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11715; 20347</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>14923; 22736</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12651; 20633</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>15535; 25371</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>31745; 43829</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>26662; 38367</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>29775; 43430</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>7484</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4948</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9060</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5421</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>7504</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>18821</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>13095</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12967</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>12925</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2179; 6396</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6056; 11493</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2664; 8507</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4695; 10768</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1806; 6729</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3854; 11152</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>9450; 16536</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>9381; 16873</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>8769; 17499</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>109734</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>91878</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>74135</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>102968</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>92515</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>63861</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>105326</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>245030</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>184393</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>137996</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>208295</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>81989; 100444</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>65034; 82201</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>85182; 132868</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>82222; 100920</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>54743; 72481</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>91608; 116618</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>171522; 198509</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>125393; 150338</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>186584; 241452</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Clase-trans_dic.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,57; 80,89</t>
+          <t>45,62; 79,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,22; 69,45</t>
+          <t>25,41; 66,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,17; 65,66</t>
+          <t>34,16; 66,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,46; 83,52</t>
+          <t>50,43; 84,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,51; 71,71</t>
+          <t>33,49; 73,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,46; 73,14</t>
+          <t>39,63; 73,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,71; 78,19</t>
+          <t>55,11; 78,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,26; 63,16</t>
+          <t>36,07; 64,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,74; 65,04</t>
+          <t>41,94; 65,3</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,73; 88,8</t>
+          <t>57,1; 88,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,34; 84,06</t>
+          <t>39,68; 84,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,34; 78,76</t>
+          <t>46,41; 79,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,02; 82,66</t>
+          <t>36,68; 82,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,63; 81,83</t>
+          <t>44,51; 80,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,07; 84,97</t>
+          <t>50,75; 84,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57,47; 82,06</t>
+          <t>57,54; 81,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49,71; 78,74</t>
+          <t>50,02; 78,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,19; 78,05</t>
+          <t>54,04; 78,13</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,24; 94,54</t>
+          <t>56,94; 94,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,56; 91,91</t>
+          <t>44,66; 91,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,17; 78,98</t>
+          <t>29,68; 77,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,37; 94,09</t>
+          <t>53,52; 94,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,9; 76,49</t>
+          <t>28,04; 80,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,61; 71,09</t>
+          <t>29,01; 72,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,26; 91,02</t>
+          <t>62,03; 90,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,52; 80,26</t>
+          <t>42,66; 78,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,53; 67,79</t>
+          <t>34,31; 66,03</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,87; 69,06</t>
+          <t>45,21; 68,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,68; 71,32</t>
+          <t>48,19; 72,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,69; 87,62</t>
+          <t>38,76; 88,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,12; 66,39</t>
+          <t>45,33; 66,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,99; 58,44</t>
+          <t>30,92; 59,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,14; 72,26</t>
+          <t>45,55; 73,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,37; 65,18</t>
+          <t>48,62; 64,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,17; 62,27</t>
+          <t>45,02; 62,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,93; 81,96</t>
+          <t>48,37; 83,24</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,67; 80,5</t>
+          <t>51,75; 81,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,98; 73,88</t>
+          <t>41,96; 73,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,53; 70,39</t>
+          <t>38,22; 69,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,23; 81,09</t>
+          <t>52,41; 81,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,3; 80,4</t>
+          <t>49,1; 79,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,18; 70,52</t>
+          <t>41,72; 71,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,01; 77,32</t>
+          <t>55,16; 76,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,0; 73,38</t>
+          <t>50,84; 73,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,89; 66,94</t>
+          <t>43,64; 65,65</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,88; 90,64</t>
+          <t>31,01; 90,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,49; 88,24</t>
+          <t>45,45; 86,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,79; 69,61</t>
+          <t>21,8; 67,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,03; 78,06</t>
+          <t>36,36; 78,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 68,81</t>
+          <t>19,1; 68,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,19; 72,89</t>
+          <t>26,36; 73,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45,32; 79,31</t>
+          <t>45,57; 79,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41,14; 74,0</t>
+          <t>39,27; 74,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31,86; 63,59</t>
+          <t>31,76; 63,25</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59,1; 72,4</t>
+          <t>59,84; 72,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52,95; 66,93</t>
+          <t>53,31; 67,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48,57; 75,76</t>
+          <t>48,63; 75,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,82; 68,52</t>
+          <t>56,44; 69,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,77; 61,93</t>
+          <t>46,72; 61,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,09; 65,04</t>
+          <t>51,72; 65,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,97; 69,4</t>
+          <t>59,85; 69,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52,28; 62,68</t>
+          <t>52,48; 63,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,6; 68,07</t>
+          <t>52,58; 69,18</t>
         </is>
       </c>
     </row>
@@ -1932,17 +1932,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9325; 16922</t>
+          <t>9544; 16680</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4470; 11003</t>
+          <t>4026; 10530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8491; 16317</t>
+          <t>8489; 16597</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,17 +1952,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11089; 18357</t>
+          <t>11084; 18569</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5769; 12724</t>
+          <t>5942; 12958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12392; 22967</t>
+          <t>12444; 23091</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23471; 33541</t>
+          <t>23641; 33523</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12180; 21214</t>
+          <t>12116; 21810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22918; 36587</t>
+          <t>23595; 36735</t>
         </is>
       </c>
     </row>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13450; 20337</t>
+          <t>13077; 20166</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4959; 10083</t>
+          <t>4760; 10113</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10858; 18454</t>
+          <t>10875; 18689</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,17 +2160,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4233; 9992</t>
+          <t>4434; 9912</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8508; 15599</t>
+          <t>8485; 15437</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12467; 19961</t>
+          <t>11923; 19898</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20110; 28716</t>
+          <t>20134; 28481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15439; 24455</t>
+          <t>15534; 24341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25427; 36625</t>
+          <t>25358; 36664</t>
         </is>
       </c>
     </row>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6681; 10845</t>
+          <t>6532; 10853</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3765; 8130</t>
+          <t>3951; 8125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2991; 7579</t>
+          <t>2848; 7410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6785; 11741</t>
+          <t>6678; 11735</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2557; 7853</t>
+          <t>2879; 8235</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5121; 12296</t>
+          <t>5017; 12543</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15151; 21798</t>
+          <t>14855; 21768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8699; 15341</t>
+          <t>8154; 15086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9017; 18231</t>
+          <t>9227; 17758</t>
         </is>
       </c>
     </row>
@@ -2556,17 +2556,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21898; 32969</t>
+          <t>21583; 32593</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22629; 33156</t>
+          <t>22404; 33534</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29548; 66925</t>
+          <t>29608; 67793</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26583; 39110</t>
+          <t>26702; 39228</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11044; 20176</t>
+          <t>10674; 20434</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25769; 40354</t>
+          <t>25440; 41063</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52648; 69513</t>
+          <t>51847; 68896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36597; 50450</t>
+          <t>36473; 50957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>64704; 108373</t>
+          <t>63957; 110068</t>
         </is>
       </c>
     </row>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14802; 23060</t>
+          <t>14825; 23297</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10909; 19667</t>
+          <t>11169; 19438</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11715; 20347</t>
+          <t>11047; 20173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14923; 22736</t>
+          <t>14695; 22865</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12651; 20633</t>
+          <t>12600; 20511</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15535; 25371</t>
+          <t>15009; 25569</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31745; 43829</t>
+          <t>31264; 43452</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26662; 38367</t>
+          <t>26578; 38273</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29775; 43430</t>
+          <t>28316; 42598</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2179; 6396</t>
+          <t>2188; 6402</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6056; 11493</t>
+          <t>5920; 11312</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2664; 8507</t>
+          <t>2664; 8262</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4695; 10768</t>
+          <t>5016; 10845</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1806; 6729</t>
+          <t>1868; 6724</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3854; 11152</t>
+          <t>4033; 11201</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9450; 16536</t>
+          <t>9502; 16598</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9381; 16873</t>
+          <t>8955; 16999</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8769; 17499</t>
+          <t>8741; 17405</t>
         </is>
       </c>
     </row>
@@ -3180,17 +3180,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81989; 100444</t>
+          <t>83013; 101061</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65034; 82201</t>
+          <t>65472; 82714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85182; 132868</t>
+          <t>85293; 131596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>82222; 100920</t>
+          <t>83132; 102163</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54743; 72481</t>
+          <t>54675; 72480</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91608; 116618</t>
+          <t>92736; 117560</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171522; 198509</t>
+          <t>171169; 198378</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125393; 150338</t>
+          <t>125872; 151231</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>186584; 241452</t>
+          <t>186492; 245396</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,44 +654,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52,75%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>64,94%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>46,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>50,93%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,82%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56,65%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>66,93%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,62; 79,73</t>
+          <t>50,3; 83,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,41; 66,46</t>
+          <t>33,79; 72,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,16; 66,78</t>
+          <t>34,87; 69,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,43; 84,49</t>
+          <t>46,86; 81,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,49; 73,03</t>
+          <t>26,31; 67,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,63; 73,54</t>
+          <t>36,02; 66,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,11; 78,15</t>
+          <t>54,43; 78,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,07; 64,94</t>
+          <t>36,85; 63,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,94; 65,3</t>
+          <t>41,48; 64,43</t>
         </is>
       </c>
     </row>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>65,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>70,28%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>75,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>64,25%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>64,23%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>63,2%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>60,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>65,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>70,16%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70,24%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,1; 88,05</t>
+          <t>35,7; 82,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,68; 84,3</t>
+          <t>47,03; 82,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,41; 79,76</t>
+          <t>50,82; 84,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,68; 82,0</t>
+          <t>58,24; 87,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,51; 80,98</t>
+          <t>41,08; 84,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,75; 84,7</t>
+          <t>46,84; 79,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57,54; 81,39</t>
+          <t>57,18; 81,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50,02; 78,37</t>
+          <t>51,21; 78,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,04; 78,13</t>
+          <t>52,97; 78,19</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>77,12%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53,61%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52,38%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>82,08%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>73,03%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53,61%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>49,6%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>53,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>49,01%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>79,5%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,94; 94,61</t>
+          <t>53,84; 94,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,66; 91,85</t>
+          <t>28,48; 81,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 77,21</t>
+          <t>29,97; 73,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,52; 94,04</t>
+          <t>57,65; 94,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,04; 80,21</t>
+          <t>42,95; 93,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,01; 72,52</t>
+          <t>24,62; 74,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,03; 90,89</t>
+          <t>62,86; 90,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42,66; 78,93</t>
+          <t>43,76; 78,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,31; 66,03</t>
+          <t>33,6; 66,75</t>
         </is>
       </c>
     </row>
@@ -1074,44 +1074,44 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>56,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45,15%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61,92%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>57,33%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>60,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64,06%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>55,86%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>61,85%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>56,81%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>59,13%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,21; 68,27</t>
+          <t>45,71; 67,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,19; 72,13</t>
+          <t>31,94; 59,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,76; 88,76</t>
+          <t>44,24; 72,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,33; 66,59</t>
+          <t>45,13; 67,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,92; 59,19</t>
+          <t>48,84; 71,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,55; 73,53</t>
+          <t>42,64; 69,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,62; 64,6</t>
+          <t>48,74; 64,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,02; 62,9</t>
+          <t>46,1; 63,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,37; 83,24</t>
+          <t>48,8; 67,33</t>
         </is>
       </c>
     </row>
@@ -1214,44 +1214,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>67,98%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>66,48%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>58,65%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>67,45%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>58,19%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>55,73%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57,08%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67,71%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,75; 81,33</t>
+          <t>48,95; 79,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,96; 73,02</t>
+          <t>49,46; 80,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,22; 69,79</t>
+          <t>43,62; 72,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,41; 81,55</t>
+          <t>51,11; 79,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,1; 79,93</t>
+          <t>42,1; 75,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,72; 71,07</t>
+          <t>40,41; 70,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55,16; 76,66</t>
+          <t>57,09; 76,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50,84; 73,21</t>
+          <t>51,41; 74,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,64; 65,65</t>
+          <t>47,73; 68,06</t>
         </is>
       </c>
     </row>
@@ -1354,44 +1354,44 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>59,06%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39,96%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48,32%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>70,13%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>69,56%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>43,92%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>39,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>49,05%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>62,8%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,01; 90,73</t>
+          <t>35,73; 79,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,45; 86,85</t>
+          <t>15,88; 67,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,8; 67,6</t>
+          <t>25,33; 72,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,36; 78,62</t>
+          <t>29,94; 90,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,1; 68,77</t>
+          <t>44,81; 86,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,36; 73,22</t>
+          <t>22,03; 68,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45,57; 79,6</t>
+          <t>44,41; 78,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39,27; 74,55</t>
+          <t>38,87; 72,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31,76; 63,25</t>
+          <t>30,08; 63,93</t>
         </is>
       </c>
     </row>
@@ -1494,44 +1494,44 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>62,81%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54,57%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>59,23%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>66,23%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>60,36%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58,71%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>54,69%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58,74%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>64,47%</t>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>57,12%</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59,84; 72,84</t>
+          <t>56,01; 69,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,31; 67,35</t>
+          <t>46,26; 61,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48,63; 75,03</t>
+          <t>51,6; 66,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,44; 69,36</t>
+          <t>60,05; 72,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,72; 61,93</t>
+          <t>52,95; 66,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,72; 65,56</t>
+          <t>47,33; 61,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,85; 69,36</t>
+          <t>59,75; 68,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52,48; 63,05</t>
+          <t>52,47; 62,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,58; 69,18</t>
+          <t>52,23; 61,86</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15125</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9360</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15993</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>13586</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7288</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12421</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15125</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9360</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>28541</t>
         </is>
       </c>
     </row>
@@ -1932,17 +1932,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9544; 16680</t>
+          <t>11056; 18412</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4026; 10530</t>
+          <t>5996; 12781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8489; 16597</t>
+          <t>10057; 20156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,17 +1952,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11084; 18569</t>
+          <t>9803; 17000</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5942; 12958</t>
+          <t>4169; 10638</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12444; 23091</t>
+          <t>8874; 16461</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23641; 33523</t>
+          <t>23351; 33696</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12116; 21810</t>
+          <t>12377; 21465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23595; 36735</t>
+          <t>22180; 34457</t>
         </is>
       </c>
     </row>
@@ -1999,37 +1999,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7340</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12443</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15900</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>17237</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7708</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15051</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7340</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12443</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31533</t>
+          <t>30422</t>
         </is>
       </c>
     </row>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13077; 20166</t>
+          <t>4316; 9994</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4760; 10113</t>
+          <t>8965; 15731</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10875; 18689</t>
+          <t>11499; 19139</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,17 +2160,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4434; 9912</t>
+          <t>13340; 20091</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8485; 15437</t>
+          <t>4928; 10167</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11923; 19898</t>
+          <t>10761; 18171</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20134; 28481</t>
+          <t>20009; 28401</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15534; 24341</t>
+          <t>15903; 24244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25358; 36664</t>
+          <t>24153; 35658</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9623</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7871</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9416</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>6460</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9623</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5504</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>12592</t>
         </is>
       </c>
     </row>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6532; 10853</t>
+          <t>6718; 11740</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3951; 8125</t>
+          <t>2924; 8334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2848; 7410</t>
+          <t>4503; 11002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6678; 11735</t>
+          <t>6613; 10843</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2879; 8235</t>
+          <t>3799; 8236</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5017; 12543</t>
+          <t>2344; 7096</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14855; 21768</t>
+          <t>15054; 21758</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8154; 15086</t>
+          <t>8365; 14954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9227; 17758</t>
+          <t>8246; 16383</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33220</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15587</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30802</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>27370</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>28129</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48928</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33220</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15587</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34541</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83468</t>
+          <t>54564</t>
         </is>
       </c>
     </row>
@@ -2556,17 +2556,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21583; 32593</t>
+          <t>26925; 39694</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22404; 33534</t>
+          <t>11029; 20375</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29608; 67793</t>
+          <t>22006; 36175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26702; 39228</t>
+          <t>21546; 32395</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10674; 20434</t>
+          <t>22704; 33208</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25440; 41063</t>
+          <t>18139; 29368</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51847; 68896</t>
+          <t>51981; 68659</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36473; 50957</t>
+          <t>37345; 51544</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63957; 110068</t>
+          <t>45033; 62136</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19059</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17061</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18867</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>19320</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>15490</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16004</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19059</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17061</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36538</t>
+          <t>34814</t>
         </is>
       </c>
     </row>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14825; 23297</t>
+          <t>13725; 22320</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11169; 19438</t>
+          <t>12692; 20560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11047; 20173</t>
+          <t>14033; 23260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14695; 22865</t>
+          <t>14640; 22764</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12600; 20511</t>
+          <t>11208; 20007</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15009; 25569</t>
+          <t>11563; 20249</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31264; 43452</t>
+          <t>32358; 43469</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26578; 38273</t>
+          <t>26877; 39018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28316; 42598</t>
+          <t>29010; 41369</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6821</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4948</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>9060</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5421</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3907</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12289</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2188; 6402</t>
+          <t>4929; 11027</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5920; 11312</t>
+          <t>1552; 6629</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2664; 8262</t>
+          <t>3575; 10299</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5016; 10845</t>
+          <t>2112; 6403</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1868; 6724</t>
+          <t>5836; 11255</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4033; 11201</t>
+          <t>2743; 8484</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9502; 16598</t>
+          <t>9261; 16334</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8955; 16999</t>
+          <t>8864; 16625</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8741; 17405</t>
+          <t>7989; 16983</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>123</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>92515</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>63861</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>96255</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>91878</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>74135</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>102968</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>92515</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>63861</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>105326</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>208295</t>
+          <t>173222</t>
         </is>
       </c>
     </row>
@@ -3180,17 +3180,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83013; 101061</t>
+          <t>82488; 101950</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65472; 82714</t>
+          <t>54141; 72017</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85293; 131596</t>
+          <t>83852; 107725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83132; 102163</t>
+          <t>83313; 100465</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54675; 72480</t>
+          <t>65030; 82282</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>92736; 117560</t>
+          <t>66612; 85932</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171169; 198378</t>
+          <t>170904; 196952</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125872; 151231</t>
+          <t>125862; 150224</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>186492; 245396</t>
+          <t>158378; 187591</t>
         </is>
       </c>
     </row>
